--- a/docs/dossiers/dossier-meudon-9e077baf.xlsx
+++ b/docs/dossiers/dossier-meudon-9e077baf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>70/100</t>
+          <t>68/100</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">

--- a/docs/dossiers/dossier-meudon-9e077baf.xlsx
+++ b/docs/dossiers/dossier-meudon-9e077baf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-meudon-9e077baf.xlsx
+++ b/docs/dossiers/dossier-meudon-9e077baf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-meudon-9e077baf.xlsx
+++ b/docs/dossiers/dossier-meudon-9e077baf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>68/100</t>
+          <t>64/100</t>
         </is>
       </c>
       <c r="C57" s="19" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>loyer_estime</t>
+          <t>loyer_estime · fiche_non_identifiee</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-meudon-9e077baf.xlsx
+++ b/docs/dossiers/dossier-meudon-9e077baf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
